--- a/pinout.xlsx
+++ b/pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jortberends/Projects/DoeDoos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1EDC4B-2D82-F549-9CB2-9F9BE309899E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3620775-081A-4441-8A4E-6A9DE615D306}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13880" yWindow="460" windowWidth="14340" windowHeight="16160" xr2:uid="{15F7FF86-A2E9-F141-814A-10DD4D52DA9D}"/>
   </bookViews>
@@ -1325,7 +1325,7 @@
         <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
@@ -1339,7 +1339,7 @@
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -1353,7 +1353,7 @@
         <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
